--- a/data/Vaudreuil_Manufacturing_Leads.xlsx
+++ b/data/Vaudreuil_Manufacturing_Leads.xlsx
@@ -805,286 +805,314 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Corporation d'Emballage International Weber</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30 years</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1145890980</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>(450) 455-0169</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>http://www.weberintl.com/</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>269 Rue Adrien-Patenaude, Vaudreuil-Dorion, QC J7V 5V5, Canada</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Vaudreuil-Dorion</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>J7V 5V5</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONAL</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>Ébénisterie Woodcreations</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C7" s="2" t="n">
         <v>36.6</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>21 years</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>1162601955</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>(450) 455-5202</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>http://woodcreations.ca/</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>931 Bd de la Cité-des-Jeunes, Vaudreuil-Dorion, QC J7V 0H2, Canada</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Vaudreuil-Dorion</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>J7V 0H2</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>OPERATIONAL</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Soudure Boisvert</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>(450) 455-3964</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.soudureboisvert.com/</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>277 Rue Boisvert, Vaudreuil-Dorion, QC J7V 8G4, Canada</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Alt Fabrication</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10 years</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1171881515</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>(450) 424-1116</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2931 Rue du Meunier, Vaudreuil-Dorion, QC J7V 8P2, Canada</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Vaudreuil-Dorion</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>J7V 8G4</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M7" s="3" t="n">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>J7V 8P2</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONAL</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Allegiant 3D Design &amp; Manufacturing Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9 years</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1172332153</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>(450) 218-4004</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>http://allegiant3d.com/</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>169 Rue Joseph-Carrier, Vaudreuil-Dorion, QC J7V 3V1, Canada</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Vaudreuil-Dorion</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>J7V 3V1</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="M9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>OPERATIONAL</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Corporation d'Emballage International Weber</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>(450) 455-0169</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>http://www.weberintl.com/</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>269 Rue Adrien-Patenaude, Vaudreuil-Dorion, QC J7V 5V5, Canada</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Fysp - Impression 3D | 3D Printing</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3375822369</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>(450) 806-5205</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>108 Rue Claude-Vivier, Vaudreuil-Dorion, QC J7V 0Y9, Canada</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Vaudreuil-Dorion</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>J7V 5V5</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="n">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>J7V 0Y9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="M10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>OPERATIONAL</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Allegiant 3D Design &amp; Manufacturing Inc.</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>(450) 218-4004</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>http://allegiant3d.com/</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>169 Rue Joseph-Carrier, Vaudreuil-Dorion, QC J7V 3V1, Canada</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>J7V 3V1</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONAL</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Fysp - Impression 3D | 3D Printing</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>(450) 806-5205</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>108 Rue Claude-Vivier, Vaudreuil-Dorion, QC J7V 0Y9, Canada</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>J7V 0Y9</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONAL</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1092,11 +1120,11 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Alt Fabrication</t>
+          <t>Soudure Boisvert</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>12.38</v>
+        <v>13.5</v>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr">
@@ -1104,16 +1132,24 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>(450) 424-1116</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
+          <t>(450) 455-3964</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.soudureboisvert.com/</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2931 Rue du Meunier, Vaudreuil-Dorion, QC J7V 8P2, Canada</t>
+          <t>277 Rue Boisvert, Vaudreuil-Dorion, QC J7V 8G4, Canada</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1123,14 +1159,14 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>J7V 8P2</t>
+          <t>J7V 8G4</t>
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
@@ -1157,13 +1193,21 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>(438) 998-4289</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
           <t>43 Rue Brodeur, Vaudreuil-Dorion, QC J7V 1P9, Canada</t>
@@ -1210,7 +1254,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>(450) 455-3371</t>
@@ -1267,7 +1315,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>(514) 735-1163</t>
@@ -1324,7 +1376,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
           <t>(514) 453-1751</t>
@@ -1399,7 +1455,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-01 20:09</t>
+          <t>2026-02-01 20:32</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1430,7 +1486,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1529,12 +1585,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Ébénisterie Woodcreations</t>
+          <t xml:space="preserve">  5. Corporation d'Emballage International Weber</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36.60</t>
+          <t>44.50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">

--- a/data/Vaudreuil_Manufacturing_Leads.xlsx
+++ b/data/Vaudreuil_Manufacturing_Leads.xlsx
@@ -553,11 +553,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mitchel Lincoln Packaging, Vaudreuil Division</t>
+          <t>Imprimerie Des Editions Vaudreuil</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>51.25</v>
+        <v>58.5</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -566,25 +566,25 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>61 years</t>
+          <t>58 years</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1143216147</v>
+        <v>1143003271</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>(450) 510-0450</t>
+          <t>(450) 455-5661</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://mitchellincoln.ca/</t>
+          <t>https://imprimerie.editionsvaudreuil.ca/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>22401 Chem. Dumberry, Vaudreuil-Dorion, QC J7V 8P7, Canada</t>
+          <t>2891 Rue du Meunier, Vaudreuil-Dorion, QC J7V 8P2, Canada</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>J7V 8P7</t>
+          <t>J7V 8P2</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -616,11 +616,11 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Quadra Chemicals Ltd</t>
+          <t>Mitchel Lincoln Packaging, Vaudreuil Division</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>48.75</v>
+        <v>56.5</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -629,25 +629,25 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>50 years</t>
+          <t>61 years</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1143161467</v>
+        <v>1143216147</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>(450) 424-0161</t>
+          <t>(450) 510-0450</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://quadragroup.com/</t>
+          <t>https://mitchellincoln.ca/</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>3901 Rue F.-X.-Tessier, Vaudreuil-Dorion, QC J7V 5V5, Canada</t>
+          <t>22401 Chem. Dumberry, Vaudreuil-Dorion, QC J7V 8P7, Canada</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -657,14 +657,14 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>J7V 5V5</t>
+          <t>J7V 8P7</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -679,11 +679,11 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Winpak Heat Seal Packaging Inc.</t>
+          <t>Quadra Chemicals Ltd</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -692,25 +692,25 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49 years</t>
+          <t>50 years</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1144131568</v>
+        <v>1143161467</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>(450) 424-0191</t>
+          <t>(450) 424-0161</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>http://www.winpak.com/</t>
+          <t>https://quadragroup.com/</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21919 Chem. Dumberry, Vaudreuil-Dorion, QC J7V 9M1, Canada</t>
+          <t>3901 Rue F.-X.-Tessier, Vaudreuil-Dorion, QC J7V 5V5, Canada</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>J7V 9M1</t>
+          <t>J7V 5V5</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -742,11 +742,11 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imprimerie Des Editions Vaudreuil</t>
+          <t>Corporation d'Emballage International Weber</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45.75</v>
+        <v>52.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -755,25 +755,25 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58 years</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1143003271</v>
+        <v>1145890980</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-5661</t>
+          <t>(450) 455-0169</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://imprimerie.editionsvaudreuil.ca/</t>
+          <t>http://www.weberintl.com/</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2891 Rue du Meunier, Vaudreuil-Dorion, QC J7V 8P2, Canada</t>
+          <t>269 Rue Adrien-Patenaude, Vaudreuil-Dorion, QC J7V 5V5, Canada</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -783,14 +783,14 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>J7V 8P2</t>
+          <t>J7V 5V5</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
         <v>5</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -805,11 +805,11 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Corporation d'Emballage International Weber</t>
+          <t>Winpak Heat Seal Packaging Inc.</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>44.5</v>
+        <v>51.25</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -818,25 +818,25 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>49 years</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1145890980</v>
+        <v>1144131568</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>(450) 455-0169</t>
+          <t>(450) 424-0191</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>http://www.weberintl.com/</t>
+          <t>http://www.winpak.com/</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>269 Rue Adrien-Patenaude, Vaudreuil-Dorion, QC J7V 5V5, Canada</t>
+          <t>21919 Chem. Dumberry, Vaudreuil-Dorion, QC J7V 9M1, Canada</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>J7V 5V5</t>
+          <t>J7V 9M1</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>36.6</v>
+        <v>49.35</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>20.27</v>
+        <v>33.02</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>19.85</v>
+        <v>32.6</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -1052,128 +1052,128 @@
       <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Soudure Boisvert</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>(450) 455-3964</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.soudureboisvert.com/</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>277 Rue Boisvert, Vaudreuil-Dorion, QC J7V 8G4, Canada</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Vaudreuil-Dorion</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>J7V 8G4</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONAL</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Fysp - Impression 3D | 3D Printing</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>14.68</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>5 years</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>3375822369</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>(450) 806-5205</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>108 Rue Claude-Vivier, Vaudreuil-Dorion, QC J7V 0Y9, Canada</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Vaudreuil-Dorion</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>J7V 0Y9</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>OPERATIONAL</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Soudure Boisvert</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>(450) 455-3964</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.soudureboisvert.com/</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>277 Rue Boisvert, Vaudreuil-Dorion, QC J7V 8G4, Canada</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Vaudreuil-Dorion</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>J7V 8G4</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONAL</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-01 20:32</t>
+          <t>2026-02-01 23:16</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12.38 - 51.25</t>
+          <t>12.38 - 58.50</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Mitchel Lincoln Packaging, Vaudreuil Division</t>
+          <t xml:space="preserve">  1. Imprimerie Des Editions Vaudreuil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>51.25</t>
+          <t>58.50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Quadra Chemicals Ltd</t>
+          <t xml:space="preserve">  2. Mitchel Lincoln Packaging, Vaudreuil Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>56.50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Winpak Heat Seal Packaging Inc.</t>
+          <t xml:space="preserve">  3. Quadra Chemicals Ltd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>46.00</t>
+          <t>54.00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Imprimerie Des Editions Vaudreuil</t>
+          <t xml:space="preserve">  4. Corporation d'Emballage International Weber</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>52.75</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Corporation d'Emballage International Weber</t>
+          <t xml:space="preserve">  5. Winpak Heat Seal Packaging Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>44.50</t>
+          <t>51.25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
